--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486695_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486695_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0875</v>
+        <v>4.9126</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6997</v>
+        <v>2.6241</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3878</v>
+        <v>2.2885</v>
       </c>
       <c r="G2" t="n">
         <v>0.3318</v>
@@ -610,13 +610,13 @@
         <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6365</v>
+        <v>1.4617</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7369</v>
+        <v>0.6614</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8996</v>
+        <v>0.8003</v>
       </c>
       <c r="V2" t="n">
         <v>3.3122</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9103</v>
+        <v>1.11</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8254</v>
+        <v>-0.4999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.915</v>
+        <v>1.6098</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0697</v>
+        <v>0.5391</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2347</v>
+        <v>0.1458</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3044</v>
+        <v>0.3933</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9651999999999999</v>
+        <v>2.2298</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9245</v>
+        <v>1.4567</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>0.7732</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0349</v>
+        <v>-1.6907</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6898</v>
+        <v>-1.3109</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3451</v>
+        <v>-0.3799</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1585</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>1.478</v>
+        <v>0.455</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5166</v>
+        <v>-0.428</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0386</v>
+        <v>0.8831</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6565</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6565</v>
+        <v>-0.3709</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8702</v>
+        <v>0.2531</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.286</v>
+        <v>-0.5946</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1561</v>
+        <v>0.8477</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5391</v>
+        <v>-0.595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1458</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3933</v>
+        <v>0.3843</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2298</v>
+        <v>0.0193</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4567</v>
+        <v>0.0554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7732</v>
+        <v>-0.0361</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6907</v>
+        <v>-0.6143</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3109</v>
+        <v>-1.0348</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3799</v>
+        <v>0.4205</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7031</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2153</v>
+        <v>0.4619</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2141</v>
+        <v>0.3514</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4294</v>
+        <v>0.1105</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0688</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0901</v>
+        <v>0.1167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0213</v>
+        <v>-0.0284</v>
       </c>
       <c r="G5" t="n">
         <v>-2.9556</v>
@@ -844,13 +844,13 @@
         <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6012</v>
+        <v>0.7584</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0555</v>
+        <v>0.1513</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6567</v>
+        <v>0.6071</v>
       </c>
       <c r="V5" t="n">
         <v>1.5133</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2428</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2613</v>
+        <v>0.6877</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5041</v>
+        <v>-0.766</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6746</v>
+        <v>-1.0697</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7587</v>
+        <v>0.2347</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4333</v>
+        <v>-1.3044</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5578</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2756</v>
+        <v>0.9245</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8334</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8832</v>
+        <v>-2.0349</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.483</v>
+        <v>-0.6898</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4002</v>
+        <v>-1.3451</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2098</v>
+        <v>0.4894</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3311</v>
+        <v>0.379</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.1104</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5133</v>
+        <v>-0.6565</v>
       </c>
       <c r="W6" t="n">
+        <v>-0.6565</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.5133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2751</v>
+        <v>-0.156</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2221</v>
+        <v>0.5716</v>
       </c>
       <c r="F7" t="n">
-        <v>0.947</v>
+        <v>-0.7276</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.595</v>
+        <v>0.6746</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-0.7587</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3843</v>
+        <v>1.4333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0193</v>
+        <v>1.5578</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0554</v>
+        <v>-0.2756</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0361</v>
+        <v>1.8334</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6143</v>
+        <v>-0.8832</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0348</v>
+        <v>-0.483</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4205</v>
+        <v>-0.4002</v>
       </c>
       <c r="P7" t="n">
         <v>0.3862</v>
@@ -1000,22 +1000,22 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.2965</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.276</v>
+        <v>-0.0208</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2098</v>
+        <v>0.3174</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4611</v>
+        <v>-0.9204</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3171</v>
+        <v>-1.6274</v>
       </c>
       <c r="F8" t="n">
-        <v>0.856</v>
+        <v>0.707</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3655</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4176</v>
+        <v>0.9584</v>
       </c>
       <c r="T8" t="n">
-        <v>0.965</v>
+        <v>0.6548</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4526</v>
+        <v>0.3036</v>
       </c>
       <c r="V8" t="n">
         <v>0.3282</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3535</v>
+        <v>-1.6833</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9789</v>
+        <v>-2.3584</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6254</v>
+        <v>0.6751</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5039</v>
@@ -1156,13 +1156,13 @@
         <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2703</v>
+        <v>0.3999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7174</v>
+        <v>-0.0968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.447</v>
+        <v>0.4967</v>
       </c>
       <c r="V9" t="n">
         <v>0.6138</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3492</v>
+        <v>-2.727</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8145</v>
+        <v>-3.8764</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5347</v>
+        <v>1.1494</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3046</v>
+        <v>-5.0493</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1864</v>
+        <v>-0.6342</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1182</v>
+        <v>-4.4151</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0212</v>
+        <v>-2.8967</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4345</v>
+        <v>-0.9097</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4558</v>
+        <v>-1.9871</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2833</v>
+        <v>-2.1525</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6209</v>
+        <v>0.2755</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6624</v>
+        <v>-2.428</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.574</v>
+        <v>0.5652</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8279</v>
+        <v>0.1788</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2539</v>
+        <v>0.3864</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8568</v>
+        <v>0.9847</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8568</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3863</v>
+        <v>-2.803</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1384</v>
+        <v>-2.4421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752</v>
+        <v>-0.3609</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.0493</v>
+        <v>-2.3046</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6342</v>
+        <v>-0.1864</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.4151</v>
+        <v>-2.1182</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8967</v>
+        <v>-1.0212</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9097</v>
+        <v>0.4345</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9871</v>
+        <v>-1.4558</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1525</v>
+        <v>-1.2833</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2755</v>
+        <v>-0.6209</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.428</v>
+        <v>-0.6624</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0941</v>
+        <v>-0.0277</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0832</v>
+        <v>-0.4555</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0109</v>
+        <v>0.4277</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9847</v>
+        <v>-0.8568</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9847</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2179</v>
+        <v>-3.6551</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6057</v>
+        <v>-3.4401</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6122</v>
+        <v>-0.2149</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5262</v>
@@ -1390,13 +1390,13 @@
         <v>2.3169</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4527</v>
+        <v>0.1101</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3039</v>
+        <v>-0.1384</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1488</v>
+        <v>0.2485</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5559</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.486699999999999</v>
+        <v>-5.658999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.6664</v>
+        <v>-10.8388</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1796</v>
+        <v>5.1797</v>
       </c>
       <c r="G13" t="n">
         <v>-20.8243</v>
@@ -1444,7 +1444,7 @@
         <v>-3.6094</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.371900000000001</v>
+        <v>-1.3719</v>
       </c>
       <c r="L13" t="n">
         <v>-2.2376</v>
@@ -1468,13 +1468,13 @@
         <v>20.2731</v>
       </c>
       <c r="S13" t="n">
-        <v>5.101099999999999</v>
+        <v>5.9288</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4093999999999996</v>
+        <v>1.2372</v>
       </c>
       <c r="U13" t="n">
-        <v>4.6915</v>
+        <v>4.691699999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.513200000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.042899999999999</v>
+        <v>8.4732</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5502</v>
+        <v>4.2399</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4927</v>
+        <v>4.2333</v>
       </c>
       <c r="G14" t="n">
         <v>8.1317</v>
@@ -1546,13 +1546,13 @@
         <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6183</v>
+        <v>0.0486</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4693</v>
+        <v>-0.7796</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0876</v>
+        <v>0.8282</v>
       </c>
       <c r="V14" t="n">
         <v>0.486</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8345</v>
+        <v>3.9817</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9166</v>
+        <v>-0.1492</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0822</v>
+        <v>4.1309</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4536</v>
+        <v>5.7177</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3797</v>
+        <v>2.2476</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8333</v>
+        <v>3.4702</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1236</v>
+        <v>4.5333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0347</v>
+        <v>2.0419</v>
       </c>
       <c r="L15" t="n">
-        <v>5.0888</v>
+        <v>2.4914</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.67</v>
+        <v>1.1845</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4145</v>
+        <v>0.2057</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2555</v>
+        <v>0.9788</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7723</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1239</v>
+        <v>-4.0546</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3809</v>
+        <v>-0.2687</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.6278</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4639</v>
+        <v>0.3592</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8107</v>
+        <v>2.3779</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4595</v>
+        <v>2.6064</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2702</v>
+        <v>-0.2285</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7177</v>
+        <v>4.4536</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2476</v>
+        <v>-0.3797</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4702</v>
+        <v>4.8333</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5333</v>
+        <v>5.1236</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0419</v>
+        <v>0.0347</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4914</v>
+        <v>5.0888</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1845</v>
+        <v>-0.67</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2057</v>
+        <v>-0.4145</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9788</v>
+        <v>-0.2555</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.7723</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-2.1239</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-4.0546</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4396</v>
+        <v>-0.0757</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9381</v>
+        <v>-0.3933</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0.3176</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.144</v>
+        <v>1.574</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9263</v>
+        <v>-1.5126</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0703</v>
+        <v>3.0866</v>
       </c>
       <c r="G17" t="n">
         <v>1.2037</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2642</v>
+        <v>0.1659</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9933</v>
+        <v>-0.5796</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7291</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>1.5559</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9172</v>
+        <v>1.2772</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5834</v>
+        <v>-1.6868</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5007</v>
+        <v>2.964</v>
       </c>
       <c r="G18" t="n">
         <v>2.8147</v>
@@ -1858,13 +1858,13 @@
         <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.739</v>
+        <v>-0.379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5245</v>
+        <v>-0.6279</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2144</v>
+        <v>0.2489</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5233</v>
+        <v>0.8902</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2163</v>
+        <v>-1.4231</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7396</v>
+        <v>2.3133</v>
       </c>
       <c r="G19" t="n">
         <v>2.6237</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8494</v>
+        <v>-0.4825</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0273</v>
+        <v>-0.1795</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8767</v>
+        <v>-0.303</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1345</v>
+        <v>-2.1842</v>
       </c>
       <c r="E20" t="n">
         <v>-1.0528</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0818</v>
+        <v>-1.1314</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9288999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5572</v>
+        <v>-0.6068</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1709</v>
+        <v>-0.2206</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1818</v>
+        <v>-3.83</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8086</v>
+        <v>-2.7052</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3732</v>
+        <v>-1.1248</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8853</v>
@@ -2092,13 +2092,13 @@
         <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9103</v>
+        <v>-0.5586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2481</v>
+        <v>0.0002</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4696</v>
+        <v>-4.0048</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5997</v>
+        <v>-3.4962</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8699</v>
+        <v>-0.5085</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3068</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3406</v>
+        <v>-0.8758</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6784</v>
+        <v>-0.317</v>
       </c>
       <c r="V22" t="n">
         <v>-0.243</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.486700000000001</v>
+        <v>8.555199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.179799999999998</v>
+        <v>-5.179600000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>11.6664</v>
+        <v>13.7349</v>
       </c>
       <c r="G23" t="n">
         <v>20.8241</v>
@@ -2248,13 +2248,13 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.101100000000001</v>
+        <v>-3.0326</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.691700000000001</v>
+        <v>-4.691599999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4094000000000001</v>
+        <v>1.659</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5133</v>
